--- a/光伏配储项目/电价数据/2026/电白站.xlsx
+++ b/光伏配储项目/电价数据/2026/电白站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50988</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38331</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7143200000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.56412</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5103</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.44979</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.44435</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43789</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.4547</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43944</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42327</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40893</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40029</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40217</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42343</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41731</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42075</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41428</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42426</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44428</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26691</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.29948</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.20823</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.25457</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.07399</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.06087</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.04757</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.02764</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.04874</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03878</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.0414</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.00046</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.02798</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08599</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.009720000000000001</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.00609</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00335</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14512</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21289</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23607</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.20932</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.10788</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.01157</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.00746</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.1447</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.18559</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.18369</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.21953</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28327</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.17431</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.11743</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.18697</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.24193</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.04159</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.2123</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.4367799999999999</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.52303</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.47074</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.74895</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.61294</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.49858</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.48371</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.06497</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.37752</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.57255</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5342</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.21666</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.49061</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.49501</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.60326</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.55926</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.42854</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48257</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40145</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41651</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42605</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6154299999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.41626</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.75176</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.09766</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.8469500000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.54392</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5268400000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50744</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51186</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50935</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39395</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47667</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38186</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39312</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37227</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37713</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42488</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.52576</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6492599999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.74582</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.44162</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38648</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.44077</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.08158</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.29614</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.25693</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.26487</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.30721</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.24093</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.57929</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.12126</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.27205</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.27836</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.25269</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.56825</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.03309</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.26849</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.30313</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.29461</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30174</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.22061</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.15208</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.22422</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.24391</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.25079</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.26687</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.42732</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.41604</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.24398</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.43882</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.24709</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.70324</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.8889900000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.85629</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.23239</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.83636</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.38316</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.8008200000000001</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43758</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.59685</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43912</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4337</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40754</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37751</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3398</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5345299999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.47313</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40165</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.38786</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39071</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43286</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44899</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39558</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.38414</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.36728</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.40338</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47402</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44853</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4429</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35472</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.28635</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.29319</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.28371</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.14362</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.38856</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.29618</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.44297</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.40929</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.25508</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.2802</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.06086</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.20671</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.13529</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.19448</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.18251</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.24444</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29208</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30061</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.2795899999999999</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.27569</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.26842</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.2284</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.18828</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>-0.006730000000000001</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.27239</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.46434</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.4905</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.28998</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.26582</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.37281</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.30174</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.31778</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34394</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.27727</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47707</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.29593</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.28002</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.2846</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.28657</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.2833</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.28365</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.28389</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.30136</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.28299</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.26608</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26371</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.19111</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.10731</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.10773</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.07919</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.25311</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.21541</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.12125</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28711</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.44177</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28909</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37467</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.20142</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06127000000000001</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.26393</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.17919</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.03512</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.02403</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.21424</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.00701</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.02587</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.04214</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.07379000000000001</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.29865</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.21237</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.17216</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.20741</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.15783</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.20322</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14627</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.20735</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.23245</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.28138</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.25434</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.28215</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41996</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.47301</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.38707</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.30174</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.26018</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29174</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.30205</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28947</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29193</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29761</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.29921</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.27728</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.27579</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.27871</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30191</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27931</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26048</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04061</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04518</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04019</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.03996</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04274</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04527</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04374</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04576</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04547</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04754</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04601</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04631</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04719</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04634000000000001</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04534000000000001</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04755</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04974</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04616</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04747999999999999</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04874</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.0484</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04615</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04722999999999999</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22008</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04661999999999999</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04939</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05204</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00222</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14696</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03743</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09877</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28976</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29277</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.36884</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38604</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37767</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40064</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39581</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41222</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46764</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41737</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35134</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.66425</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44656</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42375</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42382</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10243</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04598</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04524</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04495</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04495</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04495</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04412</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04197</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03227</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04082</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10686</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03746</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04692</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.0413</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04145</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04136</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04387</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0438</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04371</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04127</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04069</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04342</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04053</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03914</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04419</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04355</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04384</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04123</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04008</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04271</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04991</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04319</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04652000000000001</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04616</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20217</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14466</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29249</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29721</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29467</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29611</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29717</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27121</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29615</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30671</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30317</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3376</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3225</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40719</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.2834100000000001</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29346</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.29039</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28358</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27336</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27347</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28322</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17422</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.16047</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17309</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14946</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16118</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.16055</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23936</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21597</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22856</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27181</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28835</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29344</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28358</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28327</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28313</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27056</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.2830299999999999</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.40578</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.45312</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.52647</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.44111</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.43702</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39047</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.41745</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29884</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.1573</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.39992</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7910900000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62191</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49778</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78086</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92001</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49429</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.92706</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.9039199999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.3178</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.3935</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.92701</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63827</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.2259</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.88798</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5776100000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.37067</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.06024</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.57075</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8249500000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5307799999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.80714</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.80462</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.88097</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.89171</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5250499999999999</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.42982</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.44086</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.48636</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.24796</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87999</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55172</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.66249</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54844</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.5093799999999999</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.4608</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42905</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44433</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45188</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45322</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39598</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.4153</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43435</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.37376</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45129</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40069</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58949</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42852</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5968</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6019</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6470900000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45411</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.43084</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.61472</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44719</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8644299999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.83287</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8965700000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.88044</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8735499999999999</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43389</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30261</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.37642</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.45716</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29403</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27287</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31266</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31406</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45283</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41536</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37527</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35331</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.0175</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.49708</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.49145</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.6048600000000001</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.67798</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.41262</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40994</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.44351</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.50074</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.44105</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.36418</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38846</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5006499999999999</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38797</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37078</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29059</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28908</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28009</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.1647</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29688</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26104</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20106</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27748</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.28474</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.49513</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27575</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.37971</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.3787</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30515</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29034</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28989</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25543</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.25335</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27505</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.42894</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.25213</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44716</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40203</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40077</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5977</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88975</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35611</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13736</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7109</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.80467</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65149</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5902500000000001</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45105</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45035</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50045</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43765</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41506</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41294</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42369</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5009400000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.4132</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43411</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42835</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45078</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39634</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43445</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40053</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40272</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.83421</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.41623</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.39121</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.40705</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.40275</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.36631</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.16459</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.68236</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.40604</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24996</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.01105</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.9659</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.23416</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.6055499999999999</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.8061900000000001</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.27341</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26799</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.49267</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.39656</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29713</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38808</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38415</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.4767</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.42622</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.6033500000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.4654700000000001</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.6908300000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46654</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43942</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42542</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32637</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42552</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39357</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4021</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.06589</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23693</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.1462</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14881</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29558</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15574</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14472</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14203</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14471</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14353</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25865</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14532</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26829</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26847</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.1431</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.04924</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11467</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11364</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14714</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14234</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14757</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28848</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.37227</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38232</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38104</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39876</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38606</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4513</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40111</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39945</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43847</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.4416600000000001</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44109</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44604</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44534</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40411</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39174</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39892</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39264</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35057</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.59823</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39023</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47023</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4253</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41732</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38247</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38188</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39451</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38079</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38037</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.55341</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20556</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.26107</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27464</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30513</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.27445</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36871</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.43931</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.45098</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24819</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.41918</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38383</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.4178</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.49818</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36062</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42031</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39212</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38114</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28292</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.40163</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43327</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.4198</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.28215</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.26767</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.35291</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.0357</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.25205</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24993</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.20488</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07332999999999999</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.18154</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24446</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28548</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.26888</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25093</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30133</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.27185</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29512</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.42283</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.38812</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.49756</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41197</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.76574</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.4396</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.45865</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.41735</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.41498</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.3081</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35345</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.38097</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28242</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30373</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28587</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37788</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36787</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36424</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37505</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.3961</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34952</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37002</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33628</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.37632</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.70701</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.41148</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36315</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38104</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38284</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42965</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40761</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38979</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.64971</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.86861</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.48471</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.4720299999999999</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46017</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39398</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34506</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41158</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37182</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37109</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26104</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13508</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29027</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.2840299999999999</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28256</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19494</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24532</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27845</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.01308</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27958</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.12745</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.00643</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28395</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23556</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28728</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24577</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.02457</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30423</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14447</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29869</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.0403</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.22638</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.23077</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.29403</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.29535</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41541</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40642</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6419900000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.60952</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5927</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46219</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.5981799999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47552</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.71751</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.45095</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.4587</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40151</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48105</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43053</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41988</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3602</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.4926</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.46669</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.46229</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.45305</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42107</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40071</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40708</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41366</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41112</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40166</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39797</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41373</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41124</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39429</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38805</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41902</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38819</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41719</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45073</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44987</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5610599999999999</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50078</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45089</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.40067</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41811</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.3743</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42731</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.38629</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29229</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.38702</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38092</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.28907</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.26708</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.14352</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.02746</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.01681</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.29131</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.87229</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.28788</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.13667</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.09695999999999999</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.01333</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.26135</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.01942</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31406</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41185</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48515</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.42972</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5061600000000001</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50825</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.41961</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.57659</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.66989</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.6415299999999999</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.63074</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.71028</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5166799999999999</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5096700000000001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.7814099999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7220599999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5846699999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.63003</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.40382</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.41811</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.47028</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.46725</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46076</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41357</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.51597</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41754</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.43605</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.44988</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43057</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42112</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.4451</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41318</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39768</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45047</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39637</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40365</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39605</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38714</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37723</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37136</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39034</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38616</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39406</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38682</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37389</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.27409</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.2911</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15633</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.26619</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.03296</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40904</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.4539</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41396</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46482</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.01686</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18523</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.39814</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39219</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.36775</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37419</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40082</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39629</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40092</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37775</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39565</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37353</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.38966</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37641</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36302</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44366</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.42667</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.4427</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.24363</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23484</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23647</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.2434</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25098</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.03041</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.15823</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.26442</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.17203</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04341</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25867</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.02882</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14771</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.05149</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>-0.00289</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24078</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.27523</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.22102</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28356</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.38624</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37279</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36707</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37157</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35351</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31205</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31243</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30665</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.19997</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.19189</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.13541</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.15637</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.03451</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01598</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00169</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.04349</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.04689</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04166</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.00138</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.05518</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.14541</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.19604</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27654</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.2276</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.22844</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.22918</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.23352</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.24443</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.27051</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.25385</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.24784</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.23851</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29917</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.25526</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.25893</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.24219</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.25976</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.24816</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.26527</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.25361</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.26831</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.28105</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.28204</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.26415</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.22589</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.24432</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.22365</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.19627</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.10503</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>-0.01832</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.2749</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.02248</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.17559</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.17005</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.17014</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.04932</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.24114</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.2259</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.21034</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.1771</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.1673</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.14446</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.16861</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.19637</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.12218</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.13743</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.19781</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.17285</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.21769</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.1935</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.18012</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.22982</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.18219</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.2315</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.23735</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.21801</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.22371</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.14222</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.02102</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.37837</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.46263</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.23253</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.01227</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.17986</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.17436</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.02821</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.02705</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.0077</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.19137</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.03583</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.27147</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.02922</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.03737</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.09176000000000001</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04814</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.02849</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>-0.0376</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.02703</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.0412</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.03686</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>-0.02711</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23191</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.27887</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.2494</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.27833</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.16768</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32604</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.10601</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.24222</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.40124</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.24209</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.30311</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.24401</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.1057</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.2336</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39242</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.42521</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.29783</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.29229</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14797</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25378</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26977</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31156</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.18369</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.14392</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.09737</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33192</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.24556</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.26902</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37139</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37338</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.26492</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.56524</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.56859</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.2401</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.29137</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.26805</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.28048</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.27695</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.26189</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.15007</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.2575</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.26772</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.26127</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26071</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.28897</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.24105</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.27767</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36188</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.38645</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.45315</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.45206</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.49106</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.55503</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.55032</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.50868</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.3841</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.01184</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.42169</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.45557</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.40018</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.52796</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.46511</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.38352</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.4443</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.43002</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.84937</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.48705</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.42362</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45257</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.4026</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.38819</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36843</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37275</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36901</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46594</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39061</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37879</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.38201</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36424</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37253</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37776</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.28878</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.27891</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.43243</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.29333</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.19384</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.16847</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.23026</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36708</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29606</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.25375</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.18803</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.28923</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.25553</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.26637</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.33264</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.45331</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.40978</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.38786</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.46225</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5578200000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.55724</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46063</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5502400000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46122</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49353</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39494</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.53064</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.51874</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7153099999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.75936</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.5473600000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.54989</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44444</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.38945</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37535</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37658</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27258</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29999</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.29338</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.29816</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.27532</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.27253</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.28426</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.27136</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.26698</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.25982</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.2417</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.24021</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.25734</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.1929</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.21546</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.1258</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.01699</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.1574</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.009789999999999998</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.10953</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.0008399999999999999</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.02448</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.01836</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02378</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.03687</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23481</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.02141</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02058</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03144</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02169</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.00996</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01618</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.02805</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.1068</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.0598</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.11988</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.13301</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.16058</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.22473</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.18183</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.17809</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.29304</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.31156</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.20978</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.25417</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37813</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40361</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38971</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41653</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.38294</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38025</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.74925</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38355</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37436</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.29288</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.28759</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.27973</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.27337</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.26178</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.2344</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.22759</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.19667</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.19672</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.20099</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.21913</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.10211</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01237</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.009439999999999999</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.00893</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03629</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.08212</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.0459</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00361</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01302</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04471</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.02146</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.02183</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.02942</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15638</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.21243</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04184</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.17713</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.1713</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.13657</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.18861</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.12941</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.26299</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.1881</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.22019</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.18854</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.2447</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.28771</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.2652</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.41964</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39221</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.40395</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5273099999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.41251</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38751</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38959</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38643</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40796</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43136</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.38927</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38549</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.3857</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38474</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38678</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.51242</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39242</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3961</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.30259</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41766</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37093</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36459</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.27539</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.23604</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.19239</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.17675</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.11561</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.15312</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.18022</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.16841</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.09107999999999999</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.10861</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.04665</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.07364</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.03488</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.03575</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.03471</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04599</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.05377000000000001</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03623</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.05824</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.07446</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.11896</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.15249</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.08926000000000001</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.17044</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.15121</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.09262999999999999</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04663</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.21792</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.10035</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.09437000000000001</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.19127</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.13504</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.14356</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.17351</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.15109</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.18613</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.2056</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.20654</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.21948</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.25775</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.2618</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.26346</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.28589</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36188</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40187</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.27648</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38571</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.35605</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38518</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.41243</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41744</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.4961</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40819</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41766</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.44118</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41459</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39667</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.41433</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41382</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38251</v>
       </c>
     </row>
   </sheetData>
